--- a/artfynd/A 73921-2021 artfynd.xlsx
+++ b/artfynd/A 73921-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 73921-2021 artfynd.xlsx
+++ b/artfynd/A 73921-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3587,7 +3587,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>74387740</v>
+        <v>74387734</v>
       </c>
       <c r="B28" t="n">
         <v>77506</v>
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>376872.8754500371</v>
+        <v>376901.8853666277</v>
       </c>
       <c r="R28" t="n">
-        <v>6700377.027040293</v>
+        <v>6699846.171224297</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3699,7 +3699,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>74387734</v>
+        <v>74387745</v>
       </c>
       <c r="B29" t="n">
         <v>77506</v>
@@ -3739,10 +3739,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>376901.8853666277</v>
+        <v>376869.0183758087</v>
       </c>
       <c r="R29" t="n">
-        <v>6699846.171224297</v>
+        <v>6700030.180326126</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3811,7 +3811,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>74387745</v>
+        <v>74387746</v>
       </c>
       <c r="B30" t="n">
         <v>77506</v>
@@ -3851,10 +3851,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>376869.0183758087</v>
+        <v>376867.8113538623</v>
       </c>
       <c r="R30" t="n">
-        <v>6700030.180326126</v>
+        <v>6700023.795488692</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3923,10 +3923,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>74387746</v>
+        <v>74387744</v>
       </c>
       <c r="B31" t="n">
-        <v>77506</v>
+        <v>78098</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3939,21 +3939,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3963,10 +3963,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>376867.8113538623</v>
+        <v>376869.1209517682</v>
       </c>
       <c r="R31" t="n">
-        <v>6700023.795488692</v>
+        <v>6700412.245894314</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4035,10 +4035,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>74387744</v>
+        <v>74387741</v>
       </c>
       <c r="B32" t="n">
-        <v>78098</v>
+        <v>77506</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4051,21 +4051,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4075,10 +4075,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>376869.1209517682</v>
+        <v>376871.1388198495</v>
       </c>
       <c r="R32" t="n">
-        <v>6700412.245894314</v>
+        <v>6699903.072625135</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4147,7 +4147,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>74387741</v>
+        <v>74387751</v>
       </c>
       <c r="B33" t="n">
         <v>77506</v>
@@ -4187,10 +4187,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>376871.1388198495</v>
+        <v>376864.1398596731</v>
       </c>
       <c r="R33" t="n">
-        <v>6699903.072625135</v>
+        <v>6699973.996064176</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4259,7 +4259,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>74387751</v>
+        <v>74387732</v>
       </c>
       <c r="B34" t="n">
         <v>77506</v>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>376864.1398596731</v>
+        <v>376913.9812352865</v>
       </c>
       <c r="R34" t="n">
-        <v>6699973.996064176</v>
+        <v>6699837.851543591</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4371,7 +4371,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>74387732</v>
+        <v>74387737</v>
       </c>
       <c r="B35" t="n">
         <v>77506</v>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>376913.9812352865</v>
+        <v>376874.0559144435</v>
       </c>
       <c r="R35" t="n">
-        <v>6699837.851543591</v>
+        <v>6700018.146202448</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4483,7 +4483,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>74387737</v>
+        <v>74387753</v>
       </c>
       <c r="B36" t="n">
         <v>77506</v>
@@ -4523,10 +4523,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>376874.0559144435</v>
+        <v>376858.7918946482</v>
       </c>
       <c r="R36" t="n">
-        <v>6700018.146202448</v>
+        <v>6699933.150422234</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4595,10 +4595,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>74387753</v>
+        <v>112322603</v>
       </c>
       <c r="B37" t="n">
-        <v>77506</v>
+        <v>78281</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4611,34 +4611,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Jonsmyrsudden, Vrm</t>
+          <t>Gräsviggen, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>376858.7918946482</v>
+        <v>376933</v>
       </c>
       <c r="R37" t="n">
-        <v>6699933.150422234</v>
+        <v>6700074</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4665,22 +4665,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4695,22 +4685,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Per Gustafsson</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Per Gustafsson</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112322603</v>
+        <v>112323406</v>
       </c>
       <c r="B38" t="n">
-        <v>78281</v>
+        <v>77689</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4723,34 +4713,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gräsviggen, Vrm</t>
+          <t>Jonsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>376933</v>
+        <v>376867</v>
       </c>
       <c r="R38" t="n">
-        <v>6700074</v>
+        <v>6700216</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4797,19 +4787,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112323406</v>
+        <v>112323403</v>
       </c>
       <c r="B39" t="n">
         <v>77689</v>
@@ -4849,10 +4839,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>376867</v>
+        <v>376976</v>
       </c>
       <c r="R39" t="n">
-        <v>6700216</v>
+        <v>6700256</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4911,7 +4901,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112323403</v>
+        <v>112323399</v>
       </c>
       <c r="B40" t="n">
         <v>77689</v>
@@ -4951,10 +4941,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>376976</v>
+        <v>377047</v>
       </c>
       <c r="R40" t="n">
-        <v>6700256</v>
+        <v>6699906</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5013,10 +5003,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112323399</v>
+        <v>112323409</v>
       </c>
       <c r="B41" t="n">
-        <v>77689</v>
+        <v>90878</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5029,21 +5019,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5053,10 +5043,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>377047</v>
+        <v>376877</v>
       </c>
       <c r="R41" t="n">
-        <v>6699906</v>
+        <v>6700280</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5115,10 +5105,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112323409</v>
+        <v>112323395</v>
       </c>
       <c r="B42" t="n">
-        <v>90878</v>
+        <v>90855</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5127,25 +5117,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5155,10 +5145,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>376877</v>
+        <v>376769</v>
       </c>
       <c r="R42" t="n">
-        <v>6700280</v>
+        <v>6699865</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5217,10 +5207,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112323395</v>
+        <v>112323405</v>
       </c>
       <c r="B43" t="n">
-        <v>90855</v>
+        <v>77689</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5229,25 +5219,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5257,10 +5247,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>376769</v>
+        <v>376903</v>
       </c>
       <c r="R43" t="n">
-        <v>6699865</v>
+        <v>6700268</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5319,7 +5309,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112323405</v>
+        <v>112322582</v>
       </c>
       <c r="B44" t="n">
         <v>77689</v>
@@ -5355,14 +5345,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Jonsmyren, Vrm</t>
+          <t>Gräsviggen, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>376903</v>
+        <v>376995</v>
       </c>
       <c r="R44" t="n">
-        <v>6700268</v>
+        <v>6700394</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5409,19 +5399,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>112322582</v>
+        <v>112323398</v>
       </c>
       <c r="B45" t="n">
         <v>77689</v>
@@ -5457,14 +5447,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gräsviggen, Vrm</t>
+          <t>Jonsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>376995</v>
+        <v>377056</v>
       </c>
       <c r="R45" t="n">
-        <v>6700394</v>
+        <v>6699887</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5511,22 +5501,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>112323398</v>
+        <v>112323401</v>
       </c>
       <c r="B46" t="n">
-        <v>77689</v>
+        <v>78281</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5539,21 +5529,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5563,10 +5553,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>377056</v>
+        <v>376945</v>
       </c>
       <c r="R46" t="n">
-        <v>6699887</v>
+        <v>6700094</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5625,10 +5615,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112323401</v>
+        <v>112323400</v>
       </c>
       <c r="B47" t="n">
-        <v>78281</v>
+        <v>77689</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5641,21 +5631,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5665,10 +5655,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>376945</v>
+        <v>376916</v>
       </c>
       <c r="R47" t="n">
-        <v>6700094</v>
+        <v>6699968</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5727,7 +5717,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>112323400</v>
+        <v>112323397</v>
       </c>
       <c r="B48" t="n">
         <v>77689</v>
@@ -5767,10 +5757,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>376916</v>
+        <v>377010</v>
       </c>
       <c r="R48" t="n">
-        <v>6699968</v>
+        <v>6699884</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5829,10 +5819,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>112323397</v>
+        <v>112323408</v>
       </c>
       <c r="B49" t="n">
-        <v>77689</v>
+        <v>90878</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5845,21 +5835,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5869,10 +5859,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>377010</v>
+        <v>376863</v>
       </c>
       <c r="R49" t="n">
-        <v>6699884</v>
+        <v>6700246</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5931,10 +5921,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>112323408</v>
+        <v>112322639</v>
       </c>
       <c r="B50" t="n">
-        <v>90878</v>
+        <v>77689</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5947,34 +5937,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Jonsmyren, Vrm</t>
+          <t>Gräsviggen, Vrm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>376863</v>
+        <v>376970</v>
       </c>
       <c r="R50" t="n">
-        <v>6700246</v>
+        <v>6699950</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6021,19 +6011,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>112322639</v>
+        <v>112322604</v>
       </c>
       <c r="B51" t="n">
         <v>77689</v>
@@ -6073,10 +6063,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>376970</v>
+        <v>377037</v>
       </c>
       <c r="R51" t="n">
-        <v>6699950</v>
+        <v>6699915</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6135,10 +6125,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>112322604</v>
+        <v>112322635</v>
       </c>
       <c r="B52" t="n">
-        <v>77689</v>
+        <v>78281</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6151,21 +6141,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6175,10 +6165,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>377037</v>
+        <v>376947</v>
       </c>
       <c r="R52" t="n">
-        <v>6699915</v>
+        <v>6699898</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6237,10 +6227,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>112322635</v>
+        <v>112323396</v>
       </c>
       <c r="B53" t="n">
-        <v>78281</v>
+        <v>77689</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6253,34 +6243,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gräsviggen, Vrm</t>
+          <t>Jonsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>376947</v>
+        <v>376970</v>
       </c>
       <c r="R53" t="n">
-        <v>6699898</v>
+        <v>6699876</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6327,22 +6317,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>112323396</v>
+        <v>112323404</v>
       </c>
       <c r="B54" t="n">
-        <v>77689</v>
+        <v>78281</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6355,21 +6345,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6379,10 +6369,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>376970</v>
+        <v>376956</v>
       </c>
       <c r="R54" t="n">
-        <v>6699876</v>
+        <v>6700282</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6441,10 +6431,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>112323404</v>
+        <v>112322577</v>
       </c>
       <c r="B55" t="n">
-        <v>78281</v>
+        <v>77442</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6457,34 +6447,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Jonsmyren, Vrm</t>
+          <t>Gräsviggen, Vrm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>376956</v>
+        <v>376932</v>
       </c>
       <c r="R55" t="n">
-        <v>6700282</v>
+        <v>6700074</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6531,117 +6521,15 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>112322577</v>
-      </c>
-      <c r="B56" t="n">
-        <v>77442</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Gräsviggen, Vrm</t>
-        </is>
-      </c>
-      <c r="Q56" t="n">
-        <v>376932</v>
-      </c>
-      <c r="R56" t="n">
-        <v>6700074</v>
-      </c>
-      <c r="S56" t="n">
-        <v>10</v>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>Torsby</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Östmark</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>2023-09-25</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>2023-09-25</t>
-        </is>
-      </c>
-      <c r="AD56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>Helena Malmestrand</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>Helena Malmestrand</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 73921-2021 artfynd.xlsx
+++ b/artfynd/A 73921-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74387750</v>
+        <v>74387759</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376865.0812535309</v>
+        <v>376839</v>
       </c>
       <c r="R2" t="n">
-        <v>6700409.911880204</v>
+        <v>6700192</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74387756</v>
+        <v>112323395</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jonsmyrsudden, Vrm</t>
+          <t>Jonsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>376851.1413453413</v>
+        <v>376769</v>
       </c>
       <c r="R3" t="n">
-        <v>6700218.119975966</v>
+        <v>6699865</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Per Gustafsson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Gustafsson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74387725</v>
+        <v>112323408</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Jonsmyrsudden, Vrm</t>
+          <t>Jonsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376996.7937296238</v>
+        <v>376863</v>
       </c>
       <c r="R4" t="n">
-        <v>6700002.117591534</v>
+        <v>6700246</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Per Gustafsson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Per Gustafsson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74387724</v>
+        <v>112323409</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jonsmyrsudden, Vrm</t>
+          <t>Jonsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>377000.7918530595</v>
+        <v>376877</v>
       </c>
       <c r="R5" t="n">
-        <v>6700265.926565454</v>
+        <v>6700280</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,31 +1051,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Per Gustafsson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Per Gustafsson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>74387739</v>
+        <v>74387719</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>376872.8419193771</v>
+        <v>377043</v>
       </c>
       <c r="R6" t="n">
-        <v>6700376.039685452</v>
+        <v>6699936</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,19 +1160,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>74387758</v>
+        <v>74387720</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>376849.9079317059</v>
+        <v>377037</v>
       </c>
       <c r="R7" t="n">
-        <v>6700079.764070438</v>
+        <v>6699938</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1228,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>74387736</v>
+        <v>74387721</v>
       </c>
       <c r="B8" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>376889.9729257529</v>
+        <v>377025</v>
       </c>
       <c r="R8" t="n">
-        <v>6700268.204837496</v>
+        <v>6699946</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1325,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,19 +1354,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>74387721</v>
+        <v>74387722</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>377025.0852994107</v>
+        <v>377017</v>
       </c>
       <c r="R9" t="n">
-        <v>6699945.796444287</v>
+        <v>6700277</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,19 +1422,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,19 +1451,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>74387738</v>
+        <v>74387723</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1611,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>376873.8805943133</v>
+        <v>377007</v>
       </c>
       <c r="R10" t="n">
-        <v>6700260.843082374</v>
+        <v>6700271</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,19 +1519,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,19 +1548,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>74387719</v>
+        <v>74387724</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1723,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>377043.0654386982</v>
+        <v>377001</v>
       </c>
       <c r="R11" t="n">
-        <v>6699935.794955891</v>
+        <v>6700266</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,19 +1616,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,19 +1645,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>74387729</v>
+        <v>74387725</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1835,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>376970.887149193</v>
+        <v>376997</v>
       </c>
       <c r="R12" t="n">
-        <v>6700260.021504997</v>
+        <v>6700002</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,19 +1713,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,19 +1742,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>74387747</v>
+        <v>74387726</v>
       </c>
       <c r="B13" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1947,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>376867.0591878957</v>
+        <v>376980</v>
       </c>
       <c r="R13" t="n">
-        <v>6700409.844704853</v>
+        <v>6700277</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,19 +1810,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,19 +1839,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>74387731</v>
+        <v>74387728</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2059,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>376967.8946852534</v>
+        <v>376971</v>
       </c>
       <c r="R14" t="n">
-        <v>6700273.962341819</v>
+        <v>6700279</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2092,19 +1907,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,19 +1936,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>74387754</v>
+        <v>74387729</v>
       </c>
       <c r="B15" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2171,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>376856.2017830843</v>
+        <v>376971</v>
       </c>
       <c r="R15" t="n">
-        <v>6699929.778228731</v>
+        <v>6700260</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2204,19 +2004,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2246,16 +2036,11 @@
         <v>74387730</v>
       </c>
       <c r="B16" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2283,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>376969.1101584906</v>
+        <v>376969</v>
       </c>
       <c r="R16" t="n">
-        <v>6700266.012934987</v>
+        <v>6700266</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2316,19 +2101,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,19 +2130,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>74387743</v>
+        <v>74387731</v>
       </c>
       <c r="B17" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2395,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>376870.2103046329</v>
+        <v>376968</v>
       </c>
       <c r="R17" t="n">
-        <v>6700386.013980007</v>
+        <v>6700274</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,19 +2198,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,19 +2227,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>74387720</v>
+        <v>74387732</v>
       </c>
       <c r="B18" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2507,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>377037.1978320775</v>
+        <v>376914</v>
       </c>
       <c r="R18" t="n">
-        <v>6699937.97113596</v>
+        <v>6699838</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2540,19 +2295,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,37 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>74387759</v>
+        <v>74387734</v>
       </c>
       <c r="B19" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>376838.8620604862</v>
+        <v>376902</v>
       </c>
       <c r="R19" t="n">
-        <v>6700191.846452983</v>
+        <v>6699846</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2652,19 +2392,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2694,16 +2424,11 @@
         <v>74387735</v>
       </c>
       <c r="B20" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2731,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>376899.2007959604</v>
+        <v>376899</v>
       </c>
       <c r="R20" t="n">
-        <v>6700292.110244696</v>
+        <v>6700292</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2764,19 +2489,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,19 +2518,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>74387749</v>
+        <v>74387737</v>
       </c>
       <c r="B21" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2843,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>376864.8522645697</v>
+        <v>376874</v>
       </c>
       <c r="R21" t="n">
-        <v>6699951.233937764</v>
+        <v>6700018</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2876,19 +2586,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,19 +2615,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>74387726</v>
+        <v>74387738</v>
       </c>
       <c r="B22" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2955,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>376979.8799874667</v>
+        <v>376874</v>
       </c>
       <c r="R22" t="n">
-        <v>6700277.015484395</v>
+        <v>6700261</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2988,19 +2683,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,19 +2712,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>74387752</v>
+        <v>74387739</v>
       </c>
       <c r="B23" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3067,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>376863.8981990077</v>
+        <v>376873</v>
       </c>
       <c r="R23" t="n">
-        <v>6700243.882853701</v>
+        <v>6700376</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3100,19 +2780,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,19 +2809,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>74387757</v>
+        <v>74387740</v>
       </c>
       <c r="B24" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3179,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>376851.2419536079</v>
+        <v>376873</v>
       </c>
       <c r="R24" t="n">
-        <v>6700221.082168487</v>
+        <v>6700377</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3212,19 +2877,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3251,19 +2906,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>74387728</v>
+        <v>74387741</v>
       </c>
       <c r="B25" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3291,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>376971.0292153726</v>
+        <v>376871</v>
       </c>
       <c r="R25" t="n">
-        <v>6700278.798573329</v>
+        <v>6699903</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3324,19 +2974,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3366,16 +3006,11 @@
         <v>74387742</v>
       </c>
       <c r="B26" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3403,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>376869.9907624553</v>
+        <v>376870</v>
       </c>
       <c r="R26" t="n">
-        <v>6700058.81623072</v>
+        <v>6700059</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3436,19 +3071,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3475,19 +3100,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>74387760</v>
+        <v>74387743</v>
       </c>
       <c r="B27" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3515,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>376837.7977669895</v>
+        <v>376870</v>
       </c>
       <c r="R27" t="n">
-        <v>6700204.239387355</v>
+        <v>6700386</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3548,19 +3168,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3587,19 +3197,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>74387734</v>
+        <v>74387745</v>
       </c>
       <c r="B28" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3627,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>376901.8853666277</v>
+        <v>376869</v>
       </c>
       <c r="R28" t="n">
-        <v>6699846.171224297</v>
+        <v>6700030</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3660,19 +3265,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3699,19 +3294,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>74387745</v>
+        <v>74387746</v>
       </c>
       <c r="B29" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3739,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>376869.0183758087</v>
+        <v>376868</v>
       </c>
       <c r="R29" t="n">
-        <v>6700030.180326126</v>
+        <v>6700024</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3772,19 +3362,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3811,19 +3391,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>74387746</v>
+        <v>74387747</v>
       </c>
       <c r="B30" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3851,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>376867.8113538623</v>
+        <v>376867</v>
       </c>
       <c r="R30" t="n">
-        <v>6700023.795488692</v>
+        <v>6700410</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3884,19 +3459,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3923,37 +3488,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>74387744</v>
+        <v>74387749</v>
       </c>
       <c r="B31" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3963,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>376869.1209517682</v>
+        <v>376865</v>
       </c>
       <c r="R31" t="n">
-        <v>6700412.245894314</v>
+        <v>6699951</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3996,19 +3556,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4035,19 +3585,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>74387741</v>
+        <v>74387750</v>
       </c>
       <c r="B32" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -4075,10 +3620,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>376871.1388198495</v>
+        <v>376865</v>
       </c>
       <c r="R32" t="n">
-        <v>6699903.072625135</v>
+        <v>6700410</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4108,19 +3653,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4150,16 +3685,11 @@
         <v>74387751</v>
       </c>
       <c r="B33" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4187,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>376864.1398596731</v>
+        <v>376864</v>
       </c>
       <c r="R33" t="n">
-        <v>6699973.996064176</v>
+        <v>6699974</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4220,19 +3750,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4259,19 +3779,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>74387732</v>
+        <v>74387752</v>
       </c>
       <c r="B34" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4299,10 +3814,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>376913.9812352865</v>
+        <v>376864</v>
       </c>
       <c r="R34" t="n">
-        <v>6699837.851543591</v>
+        <v>6700244</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4332,19 +3847,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4371,19 +3876,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>74387737</v>
+        <v>74387753</v>
       </c>
       <c r="B35" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4411,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>376874.0559144435</v>
+        <v>376859</v>
       </c>
       <c r="R35" t="n">
-        <v>6700018.146202448</v>
+        <v>6699933</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4444,19 +3944,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4483,19 +3973,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>74387753</v>
+        <v>74387754</v>
       </c>
       <c r="B36" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4523,10 +4008,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>376858.7918946482</v>
+        <v>376856</v>
       </c>
       <c r="R36" t="n">
-        <v>6699933.150422234</v>
+        <v>6699930</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4556,19 +4041,9 @@
           <t>2018-11-15</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2018-11-15</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4595,50 +4070,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112322603</v>
+        <v>74387756</v>
       </c>
       <c r="B37" t="n">
-        <v>78281</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gräsviggen, Vrm</t>
+          <t>Jonsmyrsudden, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>376933</v>
+        <v>376851</v>
       </c>
       <c r="R37" t="n">
-        <v>6700074</v>
+        <v>6700218</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4665,12 +4135,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2018-11-15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2018-11-15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4685,31 +4155,26 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Per Gustafsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Per Gustafsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112323406</v>
+        <v>74387757</v>
       </c>
       <c r="B38" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4733,14 +4198,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Jonsmyren, Vrm</t>
+          <t>Jonsmyrsudden, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>376867</v>
+        <v>376851</v>
       </c>
       <c r="R38" t="n">
-        <v>6700216</v>
+        <v>6700221</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4767,12 +4232,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2018-11-15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2018-11-15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4787,31 +4252,26 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Per Gustafsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Per Gustafsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112323403</v>
+        <v>74387758</v>
       </c>
       <c r="B39" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4835,14 +4295,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Jonsmyren, Vrm</t>
+          <t>Jonsmyrsudden, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>376976</v>
+        <v>376850</v>
       </c>
       <c r="R39" t="n">
-        <v>6700256</v>
+        <v>6700080</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4869,12 +4329,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2018-11-15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2018-11-15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4889,31 +4349,26 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Per Gustafsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Per Gustafsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112323399</v>
+        <v>74387760</v>
       </c>
       <c r="B40" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4937,14 +4392,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Jonsmyren, Vrm</t>
+          <t>Jonsmyrsudden, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>377047</v>
+        <v>376838</v>
       </c>
       <c r="R40" t="n">
-        <v>6699906</v>
+        <v>6700204</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4971,12 +4426,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2018-11-15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2018-11-15</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4991,62 +4446,57 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Per Gustafsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Per Gustafsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112323409</v>
+        <v>112322582</v>
       </c>
       <c r="B41" t="n">
-        <v>90878</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Jonsmyren, Vrm</t>
+          <t>Gräsviggen, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>376877</v>
+        <v>376995</v>
       </c>
       <c r="R41" t="n">
-        <v>6700280</v>
+        <v>6700393</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5093,62 +4543,57 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112323395</v>
+        <v>112322604</v>
       </c>
       <c r="B42" t="n">
-        <v>90855</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Jonsmyren, Vrm</t>
+          <t>Gräsviggen, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>376769</v>
+        <v>377037</v>
       </c>
       <c r="R42" t="n">
-        <v>6699865</v>
+        <v>6699915</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5195,31 +4640,26 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112323405</v>
+        <v>112322639</v>
       </c>
       <c r="B43" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -5243,14 +4683,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Jonsmyren, Vrm</t>
+          <t>Gräsviggen, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>376903</v>
+        <v>376970</v>
       </c>
       <c r="R43" t="n">
-        <v>6700268</v>
+        <v>6699949</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5297,31 +4737,26 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112322582</v>
+        <v>112323396</v>
       </c>
       <c r="B44" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -5345,14 +4780,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gräsviggen, Vrm</t>
+          <t>Jonsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>376995</v>
+        <v>376969</v>
       </c>
       <c r="R44" t="n">
-        <v>6700394</v>
+        <v>6699875</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5399,31 +4834,26 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>112323398</v>
+        <v>112323397</v>
       </c>
       <c r="B45" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -5451,10 +4881,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>377056</v>
+        <v>377009</v>
       </c>
       <c r="R45" t="n">
-        <v>6699887</v>
+        <v>6699884</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5513,37 +4943,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>112323401</v>
+        <v>112323398</v>
       </c>
       <c r="B46" t="n">
-        <v>78281</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5553,10 +4978,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>376945</v>
+        <v>377057</v>
       </c>
       <c r="R46" t="n">
-        <v>6700094</v>
+        <v>6699888</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5615,19 +5040,14 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112323400</v>
+        <v>112323399</v>
       </c>
       <c r="B47" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5655,10 +5075,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>376916</v>
+        <v>377047</v>
       </c>
       <c r="R47" t="n">
-        <v>6699968</v>
+        <v>6699906</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5717,19 +5137,14 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>112323397</v>
+        <v>112323400</v>
       </c>
       <c r="B48" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5757,10 +5172,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>377010</v>
+        <v>376917</v>
       </c>
       <c r="R48" t="n">
-        <v>6699884</v>
+        <v>6699968</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5819,37 +5234,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>112323408</v>
+        <v>112323402</v>
       </c>
       <c r="B49" t="n">
-        <v>90878</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5859,10 +5269,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>376863</v>
+        <v>377039</v>
       </c>
       <c r="R49" t="n">
-        <v>6700246</v>
+        <v>6700189</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5921,19 +5331,14 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>112322639</v>
+        <v>112323403</v>
       </c>
       <c r="B50" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -5957,14 +5362,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Gräsviggen, Vrm</t>
+          <t>Jonsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>376970</v>
+        <v>376976</v>
       </c>
       <c r="R50" t="n">
-        <v>6699950</v>
+        <v>6700257</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6011,31 +5416,26 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>112322604</v>
+        <v>112323405</v>
       </c>
       <c r="B51" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -6059,14 +5459,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gräsviggen, Vrm</t>
+          <t>Jonsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>377037</v>
+        <v>376903</v>
       </c>
       <c r="R51" t="n">
-        <v>6699915</v>
+        <v>6700268</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6113,62 +5513,57 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>112322635</v>
+        <v>112323406</v>
       </c>
       <c r="B52" t="n">
-        <v>78281</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gräsviggen, Vrm</t>
+          <t>Jonsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>376947</v>
+        <v>376868</v>
       </c>
       <c r="R52" t="n">
-        <v>6699898</v>
+        <v>6700216</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6215,27 +5610,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>112323396</v>
+        <v>74387727</v>
       </c>
       <c r="B53" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6243,34 +5633,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Jonsmyren, Vrm</t>
+          <t>Jonsmyrsudden, Vrm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>376970</v>
+        <v>376972</v>
       </c>
       <c r="R53" t="n">
-        <v>6699876</v>
+        <v>6700098</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6297,12 +5687,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2018-11-15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2018-11-15</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6317,27 +5707,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Per Gustafsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Per Gustafsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>112323404</v>
+        <v>74387736</v>
       </c>
       <c r="B54" t="n">
-        <v>78281</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6345,34 +5730,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Jonsmyren, Vrm</t>
+          <t>Jonsmyrsudden, Vrm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>376956</v>
+        <v>376890</v>
       </c>
       <c r="R54" t="n">
-        <v>6700282</v>
+        <v>6700268</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6399,12 +5784,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2018-11-15</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2018-11-15</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6419,27 +5804,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Per Gustafsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Per Gustafsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>112322577</v>
+        <v>74387744</v>
       </c>
       <c r="B55" t="n">
-        <v>77442</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6447,34 +5827,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gräsviggen, Vrm</t>
+          <t>Jonsmyrsudden, Vrm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>376932</v>
+        <v>376869</v>
       </c>
       <c r="R55" t="n">
-        <v>6700074</v>
+        <v>6700412</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6501,12 +5881,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2018-11-15</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2018-11-15</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6521,15 +5901,500 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
+          <t>Per Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Per Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>112322603</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Gräsviggen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>376933</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6700074</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Östmark</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
           <t>Helena Malmestrand</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
+      <c r="AX56" t="inlineStr">
         <is>
           <t>Helena Malmestrand</t>
         </is>
       </c>
-      <c r="AY55" t="inlineStr"/>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>112322635</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Gräsviggen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>376947</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6699898</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Östmark</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>112323401</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Jonsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>376945</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6700094</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Östmark</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>112323404</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Jonsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>376956</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6700282</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Östmark</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>112322577</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Gräsviggen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>376932</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6700074</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Östmark</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 73921-2021 artfynd.xlsx
+++ b/artfynd/A 73921-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AZ60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387759</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112323395</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112323408</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112323409</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387719</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387720</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387721</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387722</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387723</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387724</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387725</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387726</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387728</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387729</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387730</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387731</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387732</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387734</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387735</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387737</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387738</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387739</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387740</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387741</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387742</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387743</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387745</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387746</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387747</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387749</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3679,6 +3834,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387750</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3776,6 +3936,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387751</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3873,6 +4038,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387752</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3970,6 +4140,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387753</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4067,6 +4242,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387754</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4164,6 +4344,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387756</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4261,6 +4446,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387757</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4358,6 +4548,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387758</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4455,6 +4650,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387760</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4552,6 +4752,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112322582</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4649,6 +4854,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112322604</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4746,6 +4956,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112322639</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4843,6 +5058,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112323396</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4940,6 +5160,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112323397</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5037,6 +5262,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112323398</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5134,6 +5364,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112323399</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5231,6 +5466,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112323400</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5328,6 +5568,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112323402</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5425,6 +5670,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112323403</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5522,6 +5772,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112323405</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5619,6 +5874,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112323406</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5716,6 +5976,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387727</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5813,6 +6078,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387736</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5910,6 +6180,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74387744</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6007,6 +6282,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112322603</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6104,6 +6384,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112322635</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6201,6 +6486,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112323401</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6298,6 +6588,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112323404</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6395,8 +6690,74 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112322577</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>